--- a/artfynd/A 54233-2020 artfynd.xlsx
+++ b/artfynd/A 54233-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54233-2020 artfynd.xlsx
+++ b/artfynd/A 54233-2020 artfynd.xlsx
@@ -804,12 +804,7 @@
         <v>73983630</v>
       </c>
       <c r="B3" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107283</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500688.4101874061</v>
+        <v>500688</v>
       </c>
       <c r="R3" t="n">
-        <v>6257594.865065696</v>
+        <v>6257595</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +869,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +915,7 @@
         <v>74031000</v>
       </c>
       <c r="B4" t="n">
-        <v>104790</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500488.5805426266</v>
+        <v>500489</v>
       </c>
       <c r="R4" t="n">
-        <v>6257592.627665228</v>
+        <v>6257593</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +980,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1984-01-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1056,12 +1026,7 @@
         <v>74145848</v>
       </c>
       <c r="B5" t="n">
-        <v>105130</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107577</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500488.5805426266</v>
+        <v>500489</v>
       </c>
       <c r="R5" t="n">
-        <v>6257592.627665228</v>
+        <v>6257593</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1126,19 +1091,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1182,12 +1137,7 @@
         <v>74888368</v>
       </c>
       <c r="B6" t="n">
-        <v>97328</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500188.5589103997</v>
+        <v>500189</v>
       </c>
       <c r="R6" t="n">
-        <v>6257589.289226476</v>
+        <v>6257589</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1252,19 +1202,9 @@
           <t>1984-01-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 54233-2020 artfynd.xlsx
+++ b/artfynd/A 54233-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>73983630</v>
       </c>
       <c r="B3" t="n">
-        <v>107283</v>
+        <v>107292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>74031000</v>
       </c>
       <c r="B4" t="n">
-        <v>107245</v>
+        <v>107254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74145848</v>
       </c>
       <c r="B5" t="n">
-        <v>107577</v>
+        <v>107586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74888368</v>
       </c>
       <c r="B6" t="n">
-        <v>99622</v>
+        <v>99627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54233-2020 artfynd.xlsx
+++ b/artfynd/A 54233-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>73983630</v>
       </c>
       <c r="B3" t="n">
-        <v>107292</v>
+        <v>107297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>74031000</v>
       </c>
       <c r="B4" t="n">
-        <v>107254</v>
+        <v>107259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74145848</v>
       </c>
       <c r="B5" t="n">
-        <v>107586</v>
+        <v>107591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74888368</v>
       </c>
       <c r="B6" t="n">
-        <v>99627</v>
+        <v>99628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54233-2020 artfynd.xlsx
+++ b/artfynd/A 54233-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>73983630</v>
       </c>
       <c r="B3" t="n">
-        <v>107297</v>
+        <v>107325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>74031000</v>
       </c>
       <c r="B4" t="n">
-        <v>107259</v>
+        <v>107287</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74145848</v>
       </c>
       <c r="B5" t="n">
-        <v>107591</v>
+        <v>107619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74888368</v>
       </c>
       <c r="B6" t="n">
-        <v>99628</v>
+        <v>99655</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54233-2020 artfynd.xlsx
+++ b/artfynd/A 54233-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>73983630</v>
       </c>
       <c r="B3" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>74031000</v>
       </c>
       <c r="B4" t="n">
-        <v>107287</v>
+        <v>107293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74145848</v>
       </c>
       <c r="B5" t="n">
-        <v>107619</v>
+        <v>107625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74888368</v>
       </c>
       <c r="B6" t="n">
-        <v>99655</v>
+        <v>99661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54233-2020 artfynd.xlsx
+++ b/artfynd/A 54233-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>73983630</v>
       </c>
       <c r="B3" t="n">
-        <v>107331</v>
+        <v>107338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>74031000</v>
       </c>
       <c r="B4" t="n">
-        <v>107293</v>
+        <v>107300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74145848</v>
       </c>
       <c r="B5" t="n">
-        <v>107625</v>
+        <v>107632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74888368</v>
       </c>
       <c r="B6" t="n">
-        <v>99661</v>
+        <v>99668</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54233-2020 artfynd.xlsx
+++ b/artfynd/A 54233-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>73983630</v>
       </c>
       <c r="B3" t="n">
-        <v>107338</v>
+        <v>107342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>74031000</v>
       </c>
       <c r="B4" t="n">
-        <v>107300</v>
+        <v>107304</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74145848</v>
       </c>
       <c r="B5" t="n">
-        <v>107632</v>
+        <v>107636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74888368</v>
       </c>
       <c r="B6" t="n">
-        <v>99668</v>
+        <v>99672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54233-2020 artfynd.xlsx
+++ b/artfynd/A 54233-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>73983630</v>
       </c>
       <c r="B3" t="n">
-        <v>107342</v>
+        <v>107350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>74031000</v>
       </c>
       <c r="B4" t="n">
-        <v>107304</v>
+        <v>107312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74145848</v>
       </c>
       <c r="B5" t="n">
-        <v>107636</v>
+        <v>107644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74888368</v>
       </c>
       <c r="B6" t="n">
-        <v>99672</v>
+        <v>99679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54233-2020 artfynd.xlsx
+++ b/artfynd/A 54233-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>73983630</v>
       </c>
       <c r="B3" t="n">
-        <v>107353</v>
+        <v>107358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>74031000</v>
       </c>
       <c r="B4" t="n">
-        <v>107315</v>
+        <v>107320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74145848</v>
       </c>
       <c r="B5" t="n">
-        <v>107647</v>
+        <v>107652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74888368</v>
       </c>
       <c r="B6" t="n">
-        <v>99682</v>
+        <v>99687</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54233-2020 artfynd.xlsx
+++ b/artfynd/A 54233-2020 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>73983630</v>
       </c>
       <c r="B3" t="n">
-        <v>107358</v>
+        <v>107366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>74031000</v>
       </c>
       <c r="B4" t="n">
-        <v>107320</v>
+        <v>107328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>74145848</v>
       </c>
       <c r="B5" t="n">
-        <v>107652</v>
+        <v>107660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>74888368</v>
       </c>
       <c r="B6" t="n">
-        <v>99687</v>
+        <v>99695</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
